--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:18</t>
+    <t xml:space="preserve">2026-09-29 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:08</t>
+    <t xml:space="preserve">2026-09-29 18:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -507,10 +507,10 @@
         <v>17.1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>63.91</v>
+        <v>63.92</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46.82</v>
+        <v>46.81</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         <v>6.78</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>41.96</v>
+        <v>41.97</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>35.19</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:45</t>
+    <t xml:space="preserve">2026-10-05 04:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -510,7 +510,7 @@
         <v>63.92</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46.81</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="4">
